--- a/quizzes/peinture-14e-niveau1.xlsx
+++ b/quizzes/peinture-14e-niveau1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4857673F-845D-41A3-A2D1-38E10F02D6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB0D2FD-BDDB-4279-B76A-6B5FF316E531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Top 30 peintres 14e" sheetId="1" r:id="rId1"/>
@@ -421,9 +421,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Bernardo_Dadd_1347i%2C_MAdone_de_Orsanmichele.jpg/960px-Bernardo_Dadd_1347i%2C_MAdone_de_Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://commons.wikimedia.org/wiki/File:%E5%AF%8C%E6%98%A5%E5%B1%B1%E5%B1%85%E5%9C%96(%E7%84%A1%E7%94%A8%E5%B8%AB%E5%8D%B7).jpg#/media/File:Huang_Gongwang._Dwelling_in_the_Fuchun_Mountains._detail._National_Palace_Museum,_Taipei.jpg</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/09/Wga_Nardo_di_Cione_Last_Judgment_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
@@ -461,6 +458,9 @@
   </si>
   <si>
     <t>Retable de la Vierge de Sixena</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f9/Huang_Gongwang._Dwelling_in_the_Fuchun_Mountains._detail._National_Palace_Museum%2C_Taipei.jpg/1280px-Huang_Gongwang._Dwelling_in_the_Fuchun_Mountains._detail._National_Palace_Museum%2C_Taipei.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -580,7 +580,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -915,7 +915,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>91</v>
@@ -927,7 +927,7 @@
         <v>93</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1085,7 +1085,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="6" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>75</v>
@@ -1102,19 +1102,19 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="C13" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="D13" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="E13" s="8" t="s">
         <v>145</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1136,19 +1136,19 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>140</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1204,7 +1204,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>118</v>
@@ -1453,11 +1453,11 @@
     <hyperlink ref="A31" r:id="rId23" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/Autumn_Colors_on_the_Qiao_and_Hua_Mountains_%28cropped%29.jpg/1280px-Autumn_Colors_on_the_Qiao_and_Hua_Mountains_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3976C27F-780E-452D-840E-0501F2916B22}"/>
     <hyperlink ref="A6" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="A7" r:id="rId25" xr:uid="{11FEBFD1-5B1B-4F83-86C6-E3A888BBFCA4}"/>
-    <hyperlink ref="A12" r:id="rId26" location="/media/File:Huang_Gongwang._Dwelling_in_the_Fuchun_Mountains._detail._National_Palace_Museum,_Taipei.jpg" xr:uid="{89CA6453-6CBE-415C-945E-37C9408420C4}"/>
-    <hyperlink ref="A19" r:id="rId27" xr:uid="{BF0D4971-94BD-4914-A9A6-407E50A64FF8}"/>
-    <hyperlink ref="A2" r:id="rId28" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/An_Angel_offering_a_City_to_the_Prophet._Miraj-nama._1360-1370%2C_Tabriz_%28Topkapi%2C_H.2154%29.jpg/960px-An_Angel_offering_a_City_to_the_Prophet._Miraj-nama._1360-1370%2C_Tabriz_%28Topkapi%2C_H.2154%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3AB2B026-D000-4D32-AC1F-F166F31BC1F3}"/>
-    <hyperlink ref="A15" r:id="rId29" xr:uid="{E45BBC52-A61F-423F-9CEF-00BC08144A1B}"/>
-    <hyperlink ref="A13" r:id="rId30" xr:uid="{412F50A0-C79F-4023-8F3D-A12B8268A58F}"/>
+    <hyperlink ref="A19" r:id="rId26" xr:uid="{BF0D4971-94BD-4914-A9A6-407E50A64FF8}"/>
+    <hyperlink ref="A2" r:id="rId27" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/An_Angel_offering_a_City_to_the_Prophet._Miraj-nama._1360-1370%2C_Tabriz_%28Topkapi%2C_H.2154%29.jpg/960px-An_Angel_offering_a_City_to_the_Prophet._Miraj-nama._1360-1370%2C_Tabriz_%28Topkapi%2C_H.2154%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3AB2B026-D000-4D32-AC1F-F166F31BC1F3}"/>
+    <hyperlink ref="A15" r:id="rId28" xr:uid="{E45BBC52-A61F-423F-9CEF-00BC08144A1B}"/>
+    <hyperlink ref="A13" r:id="rId29" xr:uid="{412F50A0-C79F-4023-8F3D-A12B8268A58F}"/>
+    <hyperlink ref="A12" r:id="rId30" display="https://upload.wikimedia.org/wikipedia/commons/thumb/f/f9/Huang_Gongwang._Dwelling_in_the_Fuchun_Mountains._detail._National_Palace_Museum%2C_Taipei.jpg/1280px-Huang_Gongwang._Dwelling_in_the_Fuchun_Mountains._detail._National_Palace_Museum%2C_Taipei.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{86EBFA87-43A9-46CD-B281-C8AE6DFF0D3A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/peinture-14e-niveau1.xlsx
+++ b/quizzes/peinture-14e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66B7C042-2370-418B-AB35-8881F355AE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABEBFFAF-AE3A-4427-88EB-8C82A6161087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="207">
   <si>
     <t>image</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Dimensions</t>
   </si>
   <si>
+    <t>Nationalité</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/An_Angel_offering_a_City_to_the_Prophet._Miraj-nama._1360-1370%2C_Tabriz_%28Topkapi%2C_H.2154%29.jpg/960px-An_Angel_offering_a_City_to_the_Prophet._Miraj-nama._1360-1370%2C_Tabriz_%28Topkapi%2C_H.2154%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -70,6 +73,9 @@
     <t>dimensions non standardisées</t>
   </si>
   <si>
+    <t>persane</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/68/Padova%2C_basilica_di_Sant%27Antonio_-_Cappella_di_San_Giacomo_-_Affreschi_03.jpg/1280px-Padova%2C_basilica_di_Sant%27Antonio_-_Cappella_di_San_Giacomo_-_Affreschi_03.jpg</t>
   </si>
   <si>
@@ -94,6 +100,9 @@
     <t>dimensions architecturales</t>
   </si>
   <si>
+    <t>italienne</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Ambrogio_Lorenzetti_-_Effects_of_Good_Government_in_the_city_-_Google_Art_Project.jpg/1280px-Ambrogio_Lorenzetti_-_Effects_of_Good_Government_in_the_city_-_Google_Art_Project.jpg</t>
   </si>
   <si>
@@ -268,6 +277,9 @@
     <t>environ 33 × 636 cm</t>
   </si>
   <si>
+    <t>chinoise</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Jaume_Serra_-_Altarpiece_of_the_Virgin_-_Google_Art_Project.jpg/1280px-Jaume_Serra_-_Altarpiece_of_the_Virgin_-_Google_Art_Project.jpg</t>
   </si>
   <si>
@@ -286,6 +298,9 @@
     <t>actif 1358-vers 1389</t>
   </si>
   <si>
+    <t>catalane (Espagne)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f1/4_Jean_Pucelle._Hours_of_Jeanne_d%27Evreux._1325-28%2C_Metropolitan_Museum%2C_New-York.jpg/1280px-4_Jean_Pucelle._Hours_of_Jeanne_d%27Evreux._1325-28%2C_Metropolitan_Museum%2C_New-York.jpg</t>
   </si>
   <si>
@@ -310,6 +325,9 @@
     <t>petit format manuscrit</t>
   </si>
   <si>
+    <t>française</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d9/Measta._lippo_memmi%2C_palazzo_comunale_in_san_gimignano.jpg/1280px-Measta._lippo_memmi%2C_palazzo_comunale_in_san_gimignano.jpg</t>
   </si>
   <si>
@@ -364,6 +382,9 @@
     <t>53 × 37 cm (chaque panneau)</t>
   </si>
   <si>
+    <t>anglaise (Royaume-Uni)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a7/Melchior_Broederlam_004.jpg/1280px-Melchior_Broederlam_004.jpg</t>
   </si>
   <si>
@@ -382,6 +403,9 @@
     <t>actif 1381-1409</t>
   </si>
   <si>
+    <t>flamande (Belgique)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/09/Wga_Nardo_di_Cione_Last_Judgment_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
@@ -539,6 +563,9 @@
   </si>
   <si>
     <t>vers 1340-vers 1410</t>
+  </si>
+  <si>
+    <t>grecque</t>
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/Tommaso_da_modena%2C_ritratti_di_domenicani_%28il_cardinale_di_rouen%29_1352_150cm%2C_treviso%2C_ex_convento_di_san_niccol%C3%B2%2C_sala_del_capitolo.jpg/1280px-Tommaso_da_modena%2C_ritratti_di_domenicani_%28il_cardinale_di_rouen%29_1352_150cm%2C_treviso%2C_ex_convento_di_san_niccol%C3%B2%2C_sala_del_capitolo.jpg</t>
@@ -1039,7 +1066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="46.85546875" customWidth="1"/>
@@ -1050,7 +1077,7 @@
     <col min="8" max="8" width="37.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="7" customFormat="1" ht="24.95" customHeight="1">
+    <row r="1" spans="1:9" s="7" customFormat="1" ht="24.95" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1075,785 +1102,878 @@
       <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="H10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="I10" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="2" t="s">
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="I17" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="E19" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="H21" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="E24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="I29" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" s="1" t="s">
+      <c r="H30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="3" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>197</v>
+        <v>206</v>
+      </c>
+      <c r="I31" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
